--- a/Data/Tabla auxiliar proyecciones.xlsx
+++ b/Data/Tabla auxiliar proyecciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sharo\Dropbox\UMAD\Sociodemografico\GITHUB DEFINITIVOS\Piso-I-Demografia\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shari\Dropbox\UMAD\Sociodemografico\GITHUB DEFINITIVOS\Piso-I-Demografia\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4C06EB-9D98-4D74-9406-8A7CFFCA9054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64798EC-F095-4091-8141-31B14952C789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
   <si>
     <t xml:space="preserve">Proy (NNUU 2019) </t>
   </si>
@@ -379,13 +379,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -396,7 +396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -407,7 +407,7 @@
         <v>2595.5100000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -418,7 +418,7 @@
         <v>2788.4290000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -429,7 +429,7 @@
         <v>2955.241</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -440,7 +440,7 @@
         <v>3163.7629999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -451,7 +451,7 @@
         <v>3286.3139999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -462,7 +462,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -473,7 +473,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -484,7 +484,7 @@
         <v>2810</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -506,7 +506,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -517,7 +517,7 @@
         <v>3320</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -528,7 +528,7 @@
         <v>3359</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -537,6 +537,17 @@
       </c>
       <c r="C14">
         <v>3473.7269999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>2023</v>
+      </c>
+      <c r="C15">
+        <v>3138.8130000000001</v>
       </c>
     </row>
   </sheetData>
